--- a/data/ams_weekly_data/Audio_Array/ads_report_week15.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week15.xlsx
@@ -12299,7 +12299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>46146</v>
+        <v>27764</v>
       </c>
       <c r="E6" t="n">
-        <v>360</v>
+        <v>217</v>
       </c>
       <c r="F6" t="n">
-        <v>4630.84</v>
+        <v>2786.14421749239</v>
       </c>
       <c r="G6" t="n">
-        <v>30413.57</v>
+        <v>18298.32</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -12518,28 +12518,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21383</v>
+        <v>9770</v>
       </c>
       <c r="E7" t="n">
-        <v>82.66666666666667</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>619.67</v>
+        <v>980.4138791730139</v>
       </c>
       <c r="G7" t="n">
-        <v>1176.556666666667</v>
+        <v>6438.98</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -12551,25 +12551,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0FJ2DT13L</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21383</v>
+        <v>4949</v>
       </c>
       <c r="E8" t="n">
-        <v>82.66666666666667</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
-        <v>619.67</v>
+        <v>496.6582930711522</v>
       </c>
       <c r="G8" t="n">
-        <v>1176.556666666667</v>
+        <v>3261.86</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -12584,25 +12584,25 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0G53H49BS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21383</v>
+        <v>3663</v>
       </c>
       <c r="E9" t="n">
-        <v>82.66666666666667</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>619.67</v>
+        <v>367.6236102634449</v>
       </c>
       <c r="G9" t="n">
-        <v>1176.556666666667</v>
+        <v>2414.41</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
@@ -12617,25 +12617,25 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>94329</v>
+        <v>39259</v>
       </c>
       <c r="E10" t="n">
-        <v>530</v>
+        <v>152</v>
       </c>
       <c r="F10" t="n">
-        <v>3822.39</v>
+        <v>1137.720419104335</v>
       </c>
       <c r="G10" t="n">
-        <v>8091.52</v>
+        <v>2160.17</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
@@ -12650,25 +12650,25 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>45727</v>
+        <v>10766</v>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
-        <v>3151.87</v>
+        <v>311.9952697560962</v>
       </c>
       <c r="G11" t="n">
-        <v>4321.19</v>
+        <v>592.38</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -12683,28 +12683,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0FR5DLXH9</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21971</v>
+        <v>14124</v>
       </c>
       <c r="E12" t="n">
-        <v>284</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>1877.86</v>
+        <v>409.2943111395683</v>
       </c>
       <c r="G12" t="n">
-        <v>45757.62</v>
+        <v>777.12</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -12716,28 +12716,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9559.666666666666</v>
+        <v>94329</v>
       </c>
       <c r="E13" t="n">
-        <v>34.66666666666666</v>
+        <v>530</v>
       </c>
       <c r="F13" t="n">
-        <v>369.3800000000001</v>
+        <v>3822.39</v>
       </c>
       <c r="G13" t="n">
-        <v>1073.163333333333</v>
+        <v>8091.52</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -12749,28 +12749,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9559.666666666666</v>
+        <v>45727</v>
       </c>
       <c r="E14" t="n">
-        <v>34.66666666666666</v>
+        <v>185</v>
       </c>
       <c r="F14" t="n">
-        <v>369.3800000000001</v>
+        <v>3151.87</v>
       </c>
       <c r="G14" t="n">
-        <v>1073.163333333333</v>
+        <v>4321.19</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -12782,28 +12782,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9559.666666666666</v>
+        <v>21971</v>
       </c>
       <c r="E15" t="n">
-        <v>34.66666666666666</v>
+        <v>284</v>
       </c>
       <c r="F15" t="n">
-        <v>369.3800000000001</v>
+        <v>1877.86</v>
       </c>
       <c r="G15" t="n">
-        <v>1073.163333333333</v>
+        <v>45757.62</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3333333333333333</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -12815,28 +12815,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12841.72</v>
+        <v>28679</v>
       </c>
       <c r="E16" t="n">
-        <v>52.04</v>
+        <v>104</v>
       </c>
       <c r="F16" t="n">
-        <v>487.998</v>
+        <v>1108.14</v>
       </c>
       <c r="G16" t="n">
-        <v>1657.1872</v>
+        <v>3219.49</v>
       </c>
       <c r="H16" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -12853,23 +12853,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12841.72</v>
+        <v>37678</v>
       </c>
       <c r="E17" t="n">
-        <v>52.04</v>
+        <v>136</v>
       </c>
       <c r="F17" t="n">
-        <v>487.998</v>
+        <v>1508.659907963419</v>
       </c>
       <c r="G17" t="n">
-        <v>1657.1872</v>
+        <v>8085.634348920779</v>
       </c>
       <c r="H17" t="n">
-        <v>0.96</v>
+        <v>4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -12886,23 +12886,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E18" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F18" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G18" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H18" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -12919,23 +12919,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E19" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G19" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H19" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -12952,23 +12952,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E20" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G20" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H20" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -12985,23 +12985,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4G94VP3</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12841.72</v>
+        <v>3110</v>
       </c>
       <c r="E21" t="n">
-        <v>52.04</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>487.998</v>
+        <v>139.3211309197157</v>
       </c>
       <c r="G21" t="n">
-        <v>1657.1872</v>
+        <v>656.8928482373533</v>
       </c>
       <c r="H21" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -13018,23 +13018,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E22" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G22" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H22" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -13051,23 +13051,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E23" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G23" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H23" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -13084,23 +13084,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E24" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G24" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H24" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -13117,23 +13117,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12841.72</v>
+        <v>9091</v>
       </c>
       <c r="E25" t="n">
-        <v>52.04</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n">
-        <v>487.998</v>
+        <v>463.6053923954267</v>
       </c>
       <c r="G25" t="n">
-        <v>1657.1872</v>
+        <v>1676.464216106581</v>
       </c>
       <c r="H25" t="n">
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -13150,23 +13150,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E26" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G26" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H26" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -13183,23 +13183,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12841.72</v>
+        <v>67841</v>
       </c>
       <c r="E27" t="n">
-        <v>52.04</v>
+        <v>329</v>
       </c>
       <c r="F27" t="n">
-        <v>487.998</v>
+        <v>2907.355230477083</v>
       </c>
       <c r="G27" t="n">
-        <v>1657.1872</v>
+        <v>12916.9048784456</v>
       </c>
       <c r="H27" t="n">
-        <v>0.96</v>
+        <v>4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -13216,23 +13216,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E28" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G28" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H28" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -13249,23 +13249,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E29" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F29" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G29" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H29" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -13282,23 +13282,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E30" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G30" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H30" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -13315,23 +13315,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E31" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G31" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H31" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -13348,23 +13348,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E32" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F32" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G32" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H32" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -13381,23 +13381,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E33" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F33" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G33" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H33" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -13414,23 +13414,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12841.72</v>
+        <v>26094</v>
       </c>
       <c r="E34" t="n">
-        <v>52.04</v>
+        <v>119</v>
       </c>
       <c r="F34" t="n">
-        <v>487.998</v>
+        <v>1036.986838603201</v>
       </c>
       <c r="G34" t="n">
-        <v>1657.1872</v>
+        <v>4098.202273317049</v>
       </c>
       <c r="H34" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -13447,23 +13447,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0CM9L1QZG</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12841.72</v>
+        <v>6328</v>
       </c>
       <c r="E35" t="n">
-        <v>52.04</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>487.998</v>
+        <v>289.3242729492525</v>
       </c>
       <c r="G35" t="n">
-        <v>1657.1872</v>
+        <v>1421.907285687959</v>
       </c>
       <c r="H35" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -13480,23 +13480,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12841.72</v>
+        <v>23550</v>
       </c>
       <c r="E36" t="n">
-        <v>52.04</v>
+        <v>87</v>
       </c>
       <c r="F36" t="n">
-        <v>487.998</v>
+        <v>938.409019087328</v>
       </c>
       <c r="G36" t="n">
-        <v>1657.1872</v>
+        <v>3786.45836539126</v>
       </c>
       <c r="H36" t="n">
-        <v>0.96</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -13513,23 +13513,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12841.72</v>
+        <v>6781</v>
       </c>
       <c r="E37" t="n">
-        <v>52.04</v>
+        <v>21</v>
       </c>
       <c r="F37" t="n">
-        <v>487.998</v>
+        <v>171.7416</v>
       </c>
       <c r="G37" t="n">
-        <v>1657.1872</v>
+        <v>18.61</v>
       </c>
       <c r="H37" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13546,23 +13546,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12841.72</v>
+        <v>8595</v>
       </c>
       <c r="E38" t="n">
-        <v>52.04</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>487.998</v>
+        <v>400.9727045663559</v>
       </c>
       <c r="G38" t="n">
-        <v>1657.1872</v>
+        <v>1320.695983496103</v>
       </c>
       <c r="H38" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -13579,23 +13579,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0F2HYY7JF</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12841.72</v>
+        <v>9910</v>
       </c>
       <c r="E39" t="n">
-        <v>52.04</v>
+        <v>100</v>
       </c>
       <c r="F39" t="n">
-        <v>487.998</v>
+        <v>1252.225103038217</v>
       </c>
       <c r="G39" t="n">
-        <v>1657.1872</v>
+        <v>7112.929800397317</v>
       </c>
       <c r="H39" t="n">
-        <v>0.96</v>
+        <v>7</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -13612,25 +13612,157 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>B0FF9R3GKK</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>6781</v>
+      </c>
+      <c r="E40" t="n">
+        <v>21</v>
+      </c>
+      <c r="F40" t="n">
+        <v>171.7416</v>
+      </c>
+      <c r="G40" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0G2C2RCXN</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6781</v>
+      </c>
+      <c r="E41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" t="n">
+        <v>171.7416</v>
+      </c>
+      <c r="G41" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0G3Q517Y2</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>6781</v>
+      </c>
+      <c r="E42" t="n">
+        <v>21</v>
+      </c>
+      <c r="F42" t="n">
+        <v>171.7416</v>
+      </c>
+      <c r="G42" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>6781</v>
+      </c>
+      <c r="E43" t="n">
+        <v>21</v>
+      </c>
+      <c r="F43" t="n">
+        <v>171.7416</v>
+      </c>
+      <c r="G43" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>B0G4DNF8RZ</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>12841.72</v>
-      </c>
-      <c r="E40" t="n">
-        <v>52.04</v>
-      </c>
-      <c r="F40" t="n">
-        <v>487.998</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1657.1872</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="D44" t="n">
+        <v>6781</v>
+      </c>
+      <c r="E44" t="n">
+        <v>21</v>
+      </c>
+      <c r="F44" t="n">
+        <v>171.7416</v>
+      </c>
+      <c r="G44" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week15.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week15.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
